--- a/output/yearly_surface_area_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_33_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634609161</v>
+        <v>10.84497662977865</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907199026201</v>
+        <v>37.78907297876303</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.897579443588842</v>
+        <v>5.936628367580462</v>
       </c>
       <c r="C2" t="n">
-        <v>3.515638528907828</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="D2" t="n">
-        <v>30.97512181669111</v>
+        <v>25.57452769562941</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.85923452986099</v>
+        <v>19.45333075965055</v>
       </c>
       <c r="C3" t="n">
-        <v>15.35944283294135</v>
+        <v>27.80309498426967</v>
       </c>
       <c r="D3" t="n">
-        <v>89.47648576505429</v>
+        <v>54.62444226429253</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.74984392852887</v>
+        <v>42.60195987808609</v>
       </c>
       <c r="C4" t="n">
-        <v>53.24606848753</v>
+        <v>76.14238844597412</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5296643719997</v>
+        <v>74.26626858315846</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.92249265575607</v>
+        <v>54.78152189697203</v>
       </c>
       <c r="C5" t="n">
-        <v>85.26478811383549</v>
+        <v>116.3861903384594</v>
       </c>
       <c r="D5" t="n">
-        <v>75.103699374881</v>
+        <v>58.07037670619884</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.24664932460676</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C6" t="n">
-        <v>98.61655689159213</v>
+        <v>109.4040006658561</v>
       </c>
       <c r="D6" t="n">
-        <v>48.18123208132072</v>
+        <v>44.39757642915352</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.44720359371359</v>
+        <v>32.03933632809466</v>
       </c>
       <c r="C7" t="n">
-        <v>100.0106386316226</v>
+        <v>80.6073770048886</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.69385894719101</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C8" t="n">
-        <v>73.01748550335651</v>
+        <v>49.73533869714341</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.668896450680937</v>
+        <v>7.714886530603051</v>
       </c>
       <c r="C21" t="n">
-        <v>94.9025935771766</v>
+        <v>96.43608163253813</v>
       </c>
       <c r="D21" t="n">
-        <v>7.668896450680937</v>
+        <v>8.679247346928433</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.00597260168349</v>
+        <v>8.164213908516475</v>
       </c>
       <c r="C2" t="n">
-        <v>10.28871594050657</v>
+        <v>9.107673452297659</v>
       </c>
       <c r="D2" t="n">
-        <v>27.9150142225538</v>
+        <v>24.74985962406209</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.58711048933537</v>
+        <v>19.82148614874311</v>
       </c>
       <c r="C3" t="n">
-        <v>14.40714755982194</v>
+        <v>35.74052517310513</v>
       </c>
       <c r="D3" t="n">
-        <v>92.35791527701869</v>
+        <v>60.91253630999335</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.37521721613408</v>
+        <v>39.51338160052563</v>
       </c>
       <c r="C4" t="n">
-        <v>45.35870743161113</v>
+        <v>71.93069079475531</v>
       </c>
       <c r="D4" t="n">
-        <v>126.2871159357884</v>
+        <v>82.34507044140547</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.01561981893928</v>
+        <v>58.97849333262715</v>
       </c>
       <c r="C5" t="n">
-        <v>91.37616757277189</v>
+        <v>128.3635123302705</v>
       </c>
       <c r="D5" t="n">
-        <v>92.89787651435444</v>
+        <v>70.12132977582844</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.26931163726245</v>
+        <v>60.98125864929064</v>
       </c>
       <c r="C6" t="n">
-        <v>114.8782258647363</v>
+        <v>145.831749231934</v>
       </c>
       <c r="D6" t="n">
-        <v>59.04917916733292</v>
+        <v>51.15985461600555</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.28667999630262</v>
+        <v>45.03473068920969</v>
       </c>
       <c r="C7" t="n">
-        <v>119.5336734782746</v>
+        <v>116.7788894201581</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.6242369756475</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="C8" t="n">
-        <v>101.5568912658113</v>
+        <v>77.27336180126643</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>11.87031149204818</v>
       </c>
       <c r="C9" t="n">
-        <v>65.00936947981526</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.846963243236503</v>
+        <v>7.90038675486541</v>
       </c>
       <c r="C21" t="n">
-        <v>102.9913925674791</v>
+        <v>105.6676728463249</v>
       </c>
       <c r="D21" t="n">
-        <v>8.827833648641064</v>
+        <v>9.875483443581762</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.11436575977814</v>
+        <v>9.090001993621218</v>
       </c>
       <c r="C2" t="n">
-        <v>13.15345574149877</v>
+        <v>12.28068203242335</v>
       </c>
       <c r="D2" t="n">
-        <v>29.39548976055799</v>
+        <v>25.07481811416778</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.78131660832699</v>
+        <v>23.03670988015141</v>
       </c>
       <c r="C3" t="n">
-        <v>26.12430641000763</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D3" t="n">
-        <v>92.11247835095699</v>
+        <v>64.95733685149021</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.63872651149973</v>
+        <v>37.99461790205581</v>
       </c>
       <c r="C4" t="n">
-        <v>40.55992465325273</v>
+        <v>79.89462817160542</v>
       </c>
       <c r="D4" t="n">
-        <v>137.6204114336136</v>
+        <v>91.5087035128452</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.35985341023141</v>
+        <v>59.46936718475055</v>
       </c>
       <c r="C5" t="n">
-        <v>86.83558444063038</v>
+        <v>128.7562114119692</v>
       </c>
       <c r="D5" t="n">
-        <v>111.6492576654685</v>
+        <v>80.01243789611506</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.3196428120863</v>
+        <v>68.79007988886977</v>
       </c>
       <c r="C6" t="n">
-        <v>128.282027270818</v>
+        <v>171.7940672707409</v>
       </c>
       <c r="D6" t="n">
-        <v>70.23913950033806</v>
+        <v>59.65295400544471</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>59.58717690926015</v>
+        <v>56.77250624118454</v>
       </c>
       <c r="C7" t="n">
-        <v>138.9369351050086</v>
+        <v>156.7831448728071</v>
       </c>
       <c r="D7" t="n">
-        <v>48.74770050667112</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.55461500410399</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>125.9238692852171</v>
+        <v>110.736232300519</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.41249826669968</v>
+        <v>17.63906100220244</v>
       </c>
       <c r="C9" t="n">
-        <v>91.63436721898876</v>
+        <v>67.67186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>55.8025395093887</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.010345183505235</v>
+        <v>8.069709986350617</v>
       </c>
       <c r="C21" t="n">
-        <v>111.1435394211351</v>
+        <v>113.9846535572025</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01293147938154</v>
+        <v>11.0958512312321</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.22293884432204</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C2" t="n">
-        <v>8.943721585688444</v>
+        <v>8.252571201898688</v>
       </c>
       <c r="D2" t="n">
-        <v>24.2236428545858</v>
+        <v>20.55779692692821</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34.71459882216722</v>
+        <v>27.16986771503048</v>
       </c>
       <c r="C3" t="n">
-        <v>39.40735284846697</v>
+        <v>54.13847715069036</v>
       </c>
       <c r="D3" t="n">
-        <v>101.1494659685489</v>
+        <v>70.33731427076273</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.396291581813</v>
+        <v>28.5629677073567</v>
       </c>
       <c r="C4" t="n">
-        <v>65.53656799699583</v>
+        <v>108.7511384425319</v>
       </c>
       <c r="D4" t="n">
-        <v>129.9627793404885</v>
+        <v>88.96892220195869</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61351986635881</v>
+        <v>38.75449062514284</v>
       </c>
       <c r="C5" t="n">
-        <v>76.64995200906974</v>
+        <v>102.641722479004</v>
       </c>
       <c r="D5" t="n">
-        <v>71.96210672129121</v>
+        <v>57.89857085795565</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="C6" t="n">
-        <v>91.49201380187301</v>
+        <v>103.2454973171158</v>
       </c>
       <c r="D6" t="n">
-        <v>32.08056973167303</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="C7" t="n">
-        <v>88.51240951948392</v>
+        <v>77.85259294677205</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>67.5098808825319</v>
+        <v>49.81878725200438</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>42.59999638267758</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.23900666048848</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C2" t="n">
-        <v>4.264712027248144</v>
+        <v>4.39528447191297</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76334205001429</v>
+        <v>15.50866848398686</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35.87306111317845</v>
+        <v>28.59831062470959</v>
       </c>
       <c r="C3" t="n">
-        <v>37.91509633801182</v>
+        <v>43.66813788489813</v>
       </c>
       <c r="D3" t="n">
-        <v>98.03732574608648</v>
+        <v>70.69565218281282</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.20104696185489</v>
+        <v>39.06668639509333</v>
       </c>
       <c r="C4" t="n">
-        <v>83.07254549025235</v>
+        <v>124.666250476077</v>
       </c>
       <c r="D4" t="n">
-        <v>148.9281814911284</v>
+        <v>102.3953038052381</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.69406423583604</v>
+        <v>42.95146206079796</v>
       </c>
       <c r="C5" t="n">
-        <v>99.10743074371554</v>
+        <v>150.4037482906114</v>
       </c>
       <c r="D5" t="n">
-        <v>93.36420667387168</v>
+        <v>71.37305809874313</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>42.34474197957343</v>
       </c>
       <c r="C6" t="n">
-        <v>107.9951927102619</v>
+        <v>132.6292061052229</v>
       </c>
       <c r="D6" t="n">
-        <v>40.85543071223103</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>21.73883941513712</v>
       </c>
       <c r="C7" t="n">
-        <v>109.2930631752762</v>
+        <v>104.6817942084289</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>86.86994561027902</v>
+        <v>67.59332943739288</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>47.92499593051228</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.91935781953152</v>
+        <v>6.198755004614362</v>
       </c>
       <c r="C2" t="n">
-        <v>9.098837722959438</v>
+        <v>6.137886646951058</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4380237070101</v>
+        <v>17.22476347101029</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.4559572075938</v>
+        <v>22.65873701401638</v>
       </c>
       <c r="C3" t="n">
-        <v>26.70353755551324</v>
+        <v>29.43770491184061</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18334411211201</v>
+        <v>67.49515466696822</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.38118981781757</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="C4" t="n">
-        <v>88.93063404149306</v>
+        <v>116.5108722968987</v>
       </c>
       <c r="D4" t="n">
-        <v>161.6909016463369</v>
+        <v>111.5844623169882</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.93507544946203</v>
+        <v>50.33911353525522</v>
       </c>
       <c r="C5" t="n">
-        <v>125.5655313731671</v>
+        <v>191.5880644837651</v>
       </c>
       <c r="D5" t="n">
-        <v>120.1659189998096</v>
+        <v>89.68265278294614</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.44161620712438</v>
+        <v>49.63029169278902</v>
       </c>
       <c r="C6" t="n">
-        <v>132.5889544493488</v>
+        <v>182.7425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>56.47307319138928</v>
+        <v>49.10702016642546</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99185258539232</v>
+        <v>33.41672835715293</v>
       </c>
       <c r="C7" t="n">
-        <v>132.4691812294306</v>
+        <v>146.4826479598496</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.19040230136165</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>113.9072773852362</v>
+        <v>100.3886114977576</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>57.79843259212245</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2579,7 +2579,7 @@
         <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.128249096357838</v>
+        <v>3.674681656995811</v>
       </c>
       <c r="C2" t="n">
-        <v>4.229369109895258</v>
+        <v>2.852958828541231</v>
       </c>
       <c r="D2" t="n">
-        <v>14.24319569321272</v>
+        <v>11.87227498745668</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.87319998189869</v>
+        <v>23.79265561242145</v>
       </c>
       <c r="C3" t="n">
-        <v>32.20132469929538</v>
+        <v>28.92228736711104</v>
       </c>
       <c r="D3" t="n">
-        <v>89.40776342575703</v>
+        <v>68.60943831128834</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.08612572719579</v>
+        <v>51.81664383014665</v>
       </c>
       <c r="C4" t="n">
-        <v>89.24970204537328</v>
+        <v>112.9500733735955</v>
       </c>
       <c r="D4" t="n">
-        <v>171.4160944046058</v>
+        <v>119.5101115333727</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.55495916146927</v>
+        <v>52.86711387369075</v>
       </c>
       <c r="C5" t="n">
-        <v>153.373535095958</v>
+        <v>225.6547098211294</v>
       </c>
       <c r="D5" t="n">
-        <v>126.8663470812941</v>
+        <v>94.64047868939254</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.23027840880406</v>
+        <v>40.89568236810514</v>
       </c>
       <c r="C6" t="n">
-        <v>163.2204645695535</v>
+        <v>219.089762922831</v>
       </c>
       <c r="D6" t="n">
-        <v>55.02401357992099</v>
+        <v>48.58374864006191</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>143.5482040718558</v>
+        <v>145.5843488104638</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>88.70581381722054</v>
+        <v>74.01886816168827</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2876,7 +2876,7 @@
         <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.903829782712818</v>
+        <v>4.190099201725387</v>
       </c>
       <c r="C2" t="n">
-        <v>5.099197575857933</v>
+        <v>6.163412087261475</v>
       </c>
       <c r="D2" t="n">
-        <v>15.42620167683013</v>
+        <v>10.63919987092268</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.77516408019425</v>
+        <v>18.38813450054276</v>
       </c>
       <c r="C3" t="n">
-        <v>24.21971586376881</v>
+        <v>19.58586669972387</v>
       </c>
       <c r="D3" t="n">
-        <v>80.92546326106458</v>
+        <v>62.73858703989242</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59.33388600156448</v>
+        <v>48.80464187351743</v>
       </c>
       <c r="C4" t="n">
-        <v>84.7827499910503</v>
+        <v>93.56350145783378</v>
       </c>
       <c r="D4" t="n">
-        <v>177.8102172023653</v>
+        <v>126.6317093799791</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.36109719984292</v>
+        <v>63.76451339083034</v>
       </c>
       <c r="C5" t="n">
-        <v>159.8776136365931</v>
+        <v>219.2978934361313</v>
       </c>
       <c r="D5" t="n">
-        <v>152.1954378508618</v>
+        <v>111.2074711985575</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.03659637362695</v>
+        <v>53.21268906558563</v>
       </c>
       <c r="C6" t="n">
-        <v>200.6142528766103</v>
+        <v>282.9691407950583</v>
       </c>
       <c r="D6" t="n">
-        <v>74.86807992586176</v>
+        <v>62.26931163726245</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.19419042345839</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="C7" t="n">
-        <v>186.1874703627033</v>
+        <v>220.8019309190373</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>130.7638854671539</v>
+        <v>122.0852357616121</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>61.23749480009903</v>
+        <v>51.9187455913883</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.569634652641403</v>
+        <v>3.040472640052371</v>
       </c>
       <c r="C2" t="n">
-        <v>2.723368131580652</v>
+        <v>3.134720419660066</v>
       </c>
       <c r="D2" t="n">
-        <v>11.25671917689393</v>
+        <v>8.209374302911829</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.8509385798705</v>
+        <v>16.83206438931157</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66364575253762</v>
+        <v>21.99605731364979</v>
       </c>
       <c r="D3" t="n">
-        <v>76.06581212504287</v>
+        <v>58.17836895366599</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.3864584092373</v>
+        <v>44.64399510291945</v>
       </c>
       <c r="C4" t="n">
-        <v>75.84884588240433</v>
+        <v>76.21896476690537</v>
       </c>
       <c r="D4" t="n">
-        <v>178.4866413705914</v>
+        <v>128.890710847451</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.31325360424208</v>
+        <v>68.84505776030758</v>
       </c>
       <c r="C5" t="n">
-        <v>163.8291481461865</v>
+        <v>208.7931930006905</v>
       </c>
       <c r="D5" t="n">
-        <v>172.3458094805276</v>
+        <v>125.1973759840745</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.82404014789091</v>
+        <v>62.83283481950012</v>
       </c>
       <c r="C6" t="n">
-        <v>227.9853788710114</v>
+        <v>318.4308496201572</v>
       </c>
       <c r="D6" t="n">
-        <v>90.52597406089416</v>
+        <v>73.09700706740053</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>226.3713856452295</v>
+        <v>284.8806035752267</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>164.2267559664064</v>
+        <v>163.8095131921015</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>71.33280644286897</v>
+        <v>61.23749480009903</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.215444715586557</v>
+        <v>4.117449871611123</v>
       </c>
       <c r="C2" t="n">
-        <v>4.330489123432681</v>
+        <v>5.785439221126453</v>
       </c>
       <c r="D2" t="n">
-        <v>14.46605242207675</v>
+        <v>8.988881980083795</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>13.67574552015807</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0824100538945</v>
+        <v>17.33766445699867</v>
       </c>
       <c r="D3" t="n">
-        <v>68.82051406770141</v>
+        <v>52.39587497565228</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.84369079750906</v>
+        <v>38.90077103307561</v>
       </c>
       <c r="C4" t="n">
-        <v>67.11914529624168</v>
+        <v>66.58311104972293</v>
       </c>
       <c r="D4" t="n">
-        <v>175.831995578308</v>
+        <v>128.1887612389145</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.55869053030378</v>
+        <v>68.01057221169781</v>
       </c>
       <c r="C5" t="n">
-        <v>153.1771855551086</v>
+        <v>179.3407618732861</v>
       </c>
       <c r="D5" t="n">
-        <v>190.0663555421825</v>
+        <v>137.8619213688584</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.28067600355268</v>
+        <v>74.1032984642535</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6709418682119</v>
+        <v>324.9516178717645</v>
       </c>
       <c r="D6" t="n">
-        <v>112.422874856415</v>
+        <v>88.63414623481054</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.74096714146164</v>
+        <v>38.08788393395925</v>
       </c>
       <c r="C7" t="n">
-        <v>268.2920126165683</v>
+        <v>355.0677104472396</v>
       </c>
       <c r="D7" t="n">
-        <v>57.61091878061132</v>
+        <v>51.74203100462389</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>219.0524565100695</v>
+        <v>247.5918622725243</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>118.8140524110617</v>
+        <v>112.3796779574281</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.67781649322036</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>12.29148125717007</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.962374792069131</v>
+        <v>5.546874528994478</v>
       </c>
       <c r="C2" t="n">
-        <v>8.416523068507905</v>
+        <v>2.195187866695868</v>
       </c>
       <c r="D2" t="n">
-        <v>11.30286131899353</v>
+        <v>10.24355554611122</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.447317100238051</v>
+        <v>2.949170103557418</v>
       </c>
       <c r="C2" t="n">
-        <v>2.45927799913826</v>
+        <v>3.332051708213675</v>
       </c>
       <c r="D2" t="n">
-        <v>10.64607210485241</v>
+        <v>6.615016031215008</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.01078352921349</v>
+        <v>18.30468594568178</v>
       </c>
       <c r="C3" t="n">
-        <v>19.61531913085127</v>
+        <v>21.45609607631404</v>
       </c>
       <c r="D3" t="n">
-        <v>75.24114405347555</v>
+        <v>56.48485416384024</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62.61390508145308</v>
+        <v>52.23781359526853</v>
       </c>
       <c r="C4" t="n">
-        <v>93.5890268981442</v>
+        <v>97.78796182920779</v>
       </c>
       <c r="D4" t="n">
-        <v>180.6945919574424</v>
+        <v>131.647458400976</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.16101629015904</v>
+        <v>43.61414176116455</v>
       </c>
       <c r="C5" t="n">
-        <v>215.5181647747811</v>
+        <v>270.6923857534518</v>
       </c>
       <c r="D5" t="n">
-        <v>170.4314014572463</v>
+        <v>125.7373372214103</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.92206638293279</v>
+        <v>23.62772199810799</v>
       </c>
       <c r="C6" t="n">
-        <v>224.0809682512218</v>
+        <v>297.5402402214894</v>
       </c>
       <c r="D6" t="n">
-        <v>88.07062305257288</v>
+        <v>73.05675541152641</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.485826244881928</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>154.0283608146906</v>
+        <v>174.0903751509741</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>87.53753404916685</v>
+        <v>82.78096642209104</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.60624672180155</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>10.14636252339079</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.372344421816798</v>
+        <v>6.740679737358599</v>
       </c>
       <c r="C2" t="n">
-        <v>5.324017800130453</v>
+        <v>6.062292073724055</v>
       </c>
       <c r="D2" t="n">
-        <v>17.32293824143497</v>
+        <v>10.76584532477052</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.02627050830318</v>
+        <v>11.78588118948296</v>
       </c>
       <c r="C3" t="n">
-        <v>21.2057504117311</v>
+        <v>5.615596868291756</v>
       </c>
       <c r="D3" t="n">
-        <v>12.63018421513522</v>
+        <v>11.74170254279185</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39707916431446</v>
+        <v>13.3989152244815</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13764974258744</v>
+        <v>70.14726205757964</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576126960507583</v>
+        <v>1.576342967586059</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.474225198880215</v>
+        <v>6.17421131200819</v>
       </c>
       <c r="C2" t="n">
-        <v>3.818998569520092</v>
+        <v>4.957825906446392</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35631766337936</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.01984024272996</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="C3" t="n">
-        <v>20.92595231602077</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="D3" t="n">
-        <v>24.12644983186537</v>
+        <v>17.94634803363169</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.92635322664826</v>
+        <v>13.73268688700438</v>
       </c>
       <c r="C4" t="n">
-        <v>32.86400439966198</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="D4" t="n">
-        <v>21.6838615436993</v>
+        <v>21.22440361811179</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43725609468679</v>
+        <v>15.44523165531515</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12363926509477</v>
+        <v>86.16813449807402</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24994865151301</v>
+        <v>3.251627716908454</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.171266068895449</v>
+        <v>5.426119561372121</v>
       </c>
       <c r="C2" t="n">
-        <v>4.745768402329081</v>
+        <v>5.098215828153687</v>
       </c>
       <c r="D2" t="n">
-        <v>31.99712117681204</v>
+        <v>17.48787185574843</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.59844949342983</v>
+        <v>20.45962215650353</v>
       </c>
       <c r="C3" t="n">
-        <v>17.44565670446582</v>
+        <v>18.4224956701914</v>
       </c>
       <c r="D3" t="n">
-        <v>32.41240045570844</v>
+        <v>27.82763867687584</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.05017661057038</v>
+        <v>26.34225440035042</v>
       </c>
       <c r="C4" t="n">
-        <v>43.85270645329653</v>
+        <v>28.8692729910817</v>
       </c>
       <c r="D4" t="n">
-        <v>28.89479843139213</v>
+        <v>25.25742318715769</v>
       </c>
     </row>
     <row r="5">
@@ -5176,10 +5176,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.4077694546277</v>
+        <v>12.32093368829747</v>
       </c>
       <c r="C5" t="n">
-        <v>36.96280106489242</v>
+        <v>12.17367153266045</v>
       </c>
       <c r="D5" t="n">
         <v>30.4587225242573</v>
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72716627171668</v>
+        <v>16.74458414468146</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0357142574718</v>
+        <v>102.1419632825569</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18179156792917</v>
+        <v>5.023375243404439</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.510950774564847</v>
+        <v>7.699847244407733</v>
       </c>
       <c r="C2" t="n">
-        <v>5.089380098815464</v>
+        <v>10.62349190765473</v>
       </c>
       <c r="D2" t="n">
-        <v>33.36665922423634</v>
+        <v>20.11895570312988</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.28919896659208</v>
+        <v>19.65458903902115</v>
       </c>
       <c r="C3" t="n">
-        <v>17.9758004647591</v>
+        <v>19.22752878767378</v>
       </c>
       <c r="D3" t="n">
-        <v>49.51935420220912</v>
+        <v>34.92567457858028</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.36022895866312</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="C4" t="n">
-        <v>43.30390948662256</v>
+        <v>38.67104207028186</v>
       </c>
       <c r="D4" t="n">
-        <v>38.10948238345269</v>
+        <v>32.82571623919635</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.01188845010476</v>
+        <v>26.21266370338984</v>
       </c>
       <c r="C5" t="n">
-        <v>60.74563920027141</v>
+        <v>34.68023765251858</v>
       </c>
       <c r="D5" t="n">
-        <v>33.57577148524092</v>
+        <v>32.81491701444964</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.17487426454295</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C6" t="n">
-        <v>36.26674194258143</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04608419244181</v>
+        <v>18.08011704485779</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7292159221204</v>
+        <v>117.9512397688342</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015361397480604</v>
+        <v>6.887663636136302</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.81176648269187</v>
+        <v>7.501534208149878</v>
       </c>
       <c r="C2" t="n">
-        <v>7.629161409701964</v>
+        <v>8.91721439767378</v>
       </c>
       <c r="D2" t="n">
-        <v>38.08493869084651</v>
+        <v>21.91849924501429</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.45333075965055</v>
+        <v>21.03885330200914</v>
       </c>
       <c r="C3" t="n">
-        <v>17.8039946165159</v>
+        <v>30.19365064411065</v>
       </c>
       <c r="D3" t="n">
-        <v>60.07805076138356</v>
+        <v>39.93258787023902</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.43083267791088</v>
+        <v>26.21462719879833</v>
       </c>
       <c r="C4" t="n">
-        <v>36.61624412529329</v>
+        <v>36.92254940901829</v>
       </c>
       <c r="D4" t="n">
-        <v>46.68603032775282</v>
+        <v>36.71834588653496</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.30516897176729</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="C5" t="n">
-        <v>52.81802648847841</v>
+        <v>40.49709280018094</v>
       </c>
       <c r="D5" t="n">
-        <v>31.66136346195964</v>
+        <v>30.26237298340794</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7912318963607</v>
+        <v>12.88052987971816</v>
       </c>
       <c r="C6" t="n">
-        <v>45.24286120251001</v>
+        <v>24.91577498607981</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.587527095496098</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>23.65521093382689</v>
+        <v>14.31289978021425</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.553926689373453</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050303612469305</v>
+        <v>7.070497245652699</v>
       </c>
       <c r="C21" t="n">
-        <v>66.97788431845839</v>
+        <v>67.16972383370063</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406439757793316</v>
+        <v>5.302872934239525</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.175013133263189</v>
+        <v>5.896376711706344</v>
       </c>
       <c r="C2" t="n">
-        <v>4.546473618366979</v>
+        <v>7.502515955854125</v>
       </c>
       <c r="D2" t="n">
-        <v>31.63191103083223</v>
+        <v>18.29781371175205</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.20008090968388</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="C3" t="n">
-        <v>25.54507526450201</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D3" t="n">
-        <v>77.55315989697679</v>
+        <v>49.1855599827652</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.68907338185679</v>
+        <v>35.87600635629119</v>
       </c>
       <c r="C4" t="n">
-        <v>41.69580674706629</v>
+        <v>62.09063355508952</v>
       </c>
       <c r="D4" t="n">
-        <v>66.88941633344794</v>
+        <v>49.77460860531329</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.38633523605029</v>
+        <v>33.30579086657305</v>
       </c>
       <c r="C5" t="n">
-        <v>62.02191121579226</v>
+        <v>58.09492039880502</v>
       </c>
       <c r="D5" t="n">
-        <v>42.41150082346221</v>
+        <v>37.18369429834795</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.47050349670826</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C6" t="n">
-        <v>68.10580173900973</v>
+        <v>48.86551023118075</v>
       </c>
       <c r="D6" t="n">
-        <v>34.85793398698726</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>48.02906118716245</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>26.28629478120835</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269706971657651</v>
+        <v>7.298081746353026</v>
       </c>
       <c r="C21" t="n">
-        <v>76.33192320240535</v>
+        <v>77.5421185550009</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452280228743239</v>
+        <v>6.385821528058898</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.406304680837938</v>
+        <v>4.916592502868026</v>
       </c>
       <c r="C2" t="n">
-        <v>2.850013585428491</v>
+        <v>6.604216806468294</v>
       </c>
       <c r="D2" t="n">
-        <v>31.49053936142069</v>
+        <v>18.2526533173567</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.74280746368311</v>
+        <v>22.20222433154161</v>
       </c>
       <c r="C3" t="n">
-        <v>20.84741249968102</v>
+        <v>30.80233422074368</v>
       </c>
       <c r="D3" t="n">
-        <v>84.8622715550943</v>
+        <v>52.41060119121597</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.38950146334128</v>
+        <v>42.65301075870693</v>
       </c>
       <c r="C4" t="n">
-        <v>54.58615410382691</v>
+        <v>74.94269275138453</v>
       </c>
       <c r="D4" t="n">
-        <v>90.71741486322226</v>
+        <v>62.77982044347079</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.2157731774186</v>
+        <v>45.11130701014094</v>
       </c>
       <c r="C5" t="n">
-        <v>69.90043654237292</v>
+        <v>90.44350725373742</v>
       </c>
       <c r="D5" t="n">
-        <v>56.42594930158544</v>
+        <v>47.27115195948392</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.94222542083224</v>
+        <v>35.94472869558847</v>
       </c>
       <c r="C6" t="n">
-        <v>85.05174886201394</v>
+        <v>73.6605302496382</v>
       </c>
       <c r="D6" t="n">
-        <v>40.69442408873454</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="C7" t="n">
-        <v>75.63678837828701</v>
+        <v>51.80191761458295</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>46.31394794784328</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.84374755077128</v>
+        <v>24.51718541815559</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.476387533725201</v>
+        <v>7.513436828787759</v>
       </c>
       <c r="C21" t="n">
-        <v>85.97845663783981</v>
+        <v>87.34370313465769</v>
       </c>
       <c r="D21" t="n">
-        <v>6.541839092009551</v>
+        <v>7.513436828787759</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_33_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497662977865</v>
+        <v>10.84497628164228</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907297876303</v>
+        <v>37.78907176568981</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.936628367580462</v>
+        <v>5.300455855228529</v>
       </c>
       <c r="C2" t="n">
-        <v>11.10945702125691</v>
+        <v>10.9101622372948</v>
       </c>
       <c r="D2" t="n">
-        <v>25.57452769562941</v>
+        <v>29.63110920957723</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.45333075965055</v>
+        <v>17.21494599396782</v>
       </c>
       <c r="C3" t="n">
-        <v>27.80309498426967</v>
+        <v>38.54341486872978</v>
       </c>
       <c r="D3" t="n">
-        <v>54.62444226429253</v>
+        <v>62.70422587024377</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.60195987808609</v>
+        <v>37.6755498981756</v>
       </c>
       <c r="C4" t="n">
-        <v>76.14238844597412</v>
+        <v>77.6101012638231</v>
       </c>
       <c r="D4" t="n">
-        <v>74.26626858315846</v>
+        <v>78.96294960027521</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.78152189697203</v>
+        <v>46.16668579220627</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3861903384594</v>
+        <v>105.7833151325938</v>
       </c>
       <c r="D5" t="n">
-        <v>58.07037670619884</v>
+        <v>61.60466844148736</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.30827844579606</v>
+        <v>42.82776185006286</v>
       </c>
       <c r="C6" t="n">
-        <v>109.4040006658561</v>
+        <v>100.8303979646687</v>
       </c>
       <c r="D6" t="n">
-        <v>44.39757642915352</v>
+        <v>44.27682146153116</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.03933632809466</v>
+        <v>30.12296480940488</v>
       </c>
       <c r="C7" t="n">
-        <v>80.6073770048886</v>
+        <v>107.1970318267092</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.27246819789088</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>49.73533869714341</v>
+        <v>78.77543578876406</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.714886530603051</v>
+        <v>7.69202780418958</v>
       </c>
       <c r="C21" t="n">
-        <v>96.43608163253813</v>
+        <v>94.22734060132234</v>
       </c>
       <c r="D21" t="n">
-        <v>8.679247346928433</v>
+        <v>8.653531279713278</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.164213908516475</v>
+        <v>6.520768251607315</v>
       </c>
       <c r="C2" t="n">
-        <v>9.107673452297659</v>
+        <v>10.54397034361074</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74985962406209</v>
+        <v>26.27549555646164</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.82148614874311</v>
+        <v>17.41129553481718</v>
       </c>
       <c r="C3" t="n">
-        <v>35.74052517310513</v>
+        <v>40.3203782134165</v>
       </c>
       <c r="D3" t="n">
-        <v>60.91253630999335</v>
+        <v>70.11151229878597</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.51338160052563</v>
+        <v>35.27615850899639</v>
       </c>
       <c r="C4" t="n">
-        <v>71.93069079475531</v>
+        <v>86.09731016703677</v>
       </c>
       <c r="D4" t="n">
-        <v>82.34507044140547</v>
+        <v>90.27071965778997</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.97849333262715</v>
+        <v>50.70726892434777</v>
       </c>
       <c r="C5" t="n">
-        <v>128.3635123302705</v>
+        <v>124.0192787389783</v>
       </c>
       <c r="D5" t="n">
-        <v>70.12132977582844</v>
+        <v>72.99294181075037</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.98125864929064</v>
+        <v>51.80388110999145</v>
       </c>
       <c r="C6" t="n">
-        <v>145.831749231934</v>
+        <v>131.6229147083699</v>
       </c>
       <c r="D6" t="n">
-        <v>51.15985461600555</v>
+        <v>52.36740429222912</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.03473068920969</v>
+        <v>40.18391528252619</v>
       </c>
       <c r="C7" t="n">
-        <v>116.7788894201581</v>
+        <v>126.420633623566</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.86766934857171</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="C8" t="n">
-        <v>77.27336180126643</v>
+        <v>108.3996727644116</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>70.77811898996953</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.90038675486541</v>
+        <v>7.872942479898646</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6676728463249</v>
+        <v>102.3482522386824</v>
       </c>
       <c r="D21" t="n">
-        <v>9.875483443581762</v>
+        <v>9.841178099873309</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.090001993621218</v>
+        <v>7.875580083467912</v>
       </c>
       <c r="C2" t="n">
-        <v>12.28068203242335</v>
+        <v>9.911724822075797</v>
       </c>
       <c r="D2" t="n">
-        <v>25.07481811416778</v>
+        <v>28.52173430377833</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.03670988015141</v>
+        <v>19.10481032464293</v>
       </c>
       <c r="C3" t="n">
-        <v>35.3036474447153</v>
+        <v>40.30074325933157</v>
       </c>
       <c r="D3" t="n">
-        <v>64.95733685149021</v>
+        <v>74.0237769002095</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.99461790205581</v>
+        <v>33.57871672835365</v>
       </c>
       <c r="C4" t="n">
-        <v>79.89462817160542</v>
+        <v>92.56800928572751</v>
       </c>
       <c r="D4" t="n">
-        <v>91.5087035128452</v>
+        <v>99.90657337497241</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.46936718475055</v>
+        <v>51.8362787842316</v>
       </c>
       <c r="C5" t="n">
-        <v>128.7562114119692</v>
+        <v>137.7882902910399</v>
       </c>
       <c r="D5" t="n">
-        <v>80.01243789611506</v>
+        <v>84.55302102825655</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.79007988886977</v>
+        <v>58.48565598509524</v>
       </c>
       <c r="C6" t="n">
-        <v>171.7940672707409</v>
+        <v>160.0405837554981</v>
       </c>
       <c r="D6" t="n">
-        <v>59.65295400544471</v>
+        <v>61.34352355215771</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.77250624118454</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="C7" t="n">
-        <v>156.7831448728071</v>
+        <v>153.0102884453866</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>46.05280305851362</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.04839304161113</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="C8" t="n">
-        <v>110.736232300519</v>
+        <v>133.8514819970101</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.63906100220244</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>98.73436661610168</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>59.50372835439919</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.069709986350617</v>
+        <v>8.037506100052498</v>
       </c>
       <c r="C21" t="n">
-        <v>113.9846535572025</v>
+        <v>110.5157088757219</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0958512312321</v>
+        <v>11.05157088757218</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.26435217434965</v>
+        <v>7.154977268550754</v>
       </c>
       <c r="C2" t="n">
-        <v>8.252571201898688</v>
+        <v>6.739697989654353</v>
       </c>
       <c r="D2" t="n">
-        <v>20.55779692692821</v>
+        <v>23.52758373227481</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.16986771503048</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="C3" t="n">
-        <v>54.13847715069036</v>
+        <v>59.33192250615598</v>
       </c>
       <c r="D3" t="n">
-        <v>70.33731427076273</v>
+        <v>79.31048828757858</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.5629677073567</v>
+        <v>24.90006702281185</v>
       </c>
       <c r="C4" t="n">
-        <v>108.7511384425319</v>
+        <v>119.4335352124415</v>
       </c>
       <c r="D4" t="n">
-        <v>88.96892220195869</v>
+        <v>95.60553668266714</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.75449062514284</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C5" t="n">
-        <v>102.641722479004</v>
+        <v>95.62222639363934</v>
       </c>
       <c r="D5" t="n">
-        <v>57.89857085795565</v>
+        <v>59.37119241432587</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.22019888985433</v>
+        <v>30.43025184083414</v>
       </c>
       <c r="C6" t="n">
-        <v>103.2454973171158</v>
+        <v>100.7498946529204</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="C7" t="n">
-        <v>77.85259294677205</v>
+        <v>94.08186424567607</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>49.81878725200438</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>45.37343364717482</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.959789401854886</v>
+        <v>4.493459242337651</v>
       </c>
       <c r="C2" t="n">
-        <v>4.39528447191297</v>
+        <v>4.010439371848221</v>
       </c>
       <c r="D2" t="n">
-        <v>15.50866848398686</v>
+        <v>16.45016453235955</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.59831062470959</v>
+        <v>24.40624792757571</v>
       </c>
       <c r="C3" t="n">
-        <v>43.66813788489813</v>
+        <v>43.36379609658162</v>
       </c>
       <c r="D3" t="n">
-        <v>70.69565218281282</v>
+        <v>79.95353303386024</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.06668639509333</v>
+        <v>33.25964872447344</v>
       </c>
       <c r="C4" t="n">
-        <v>124.666250476077</v>
+        <v>136.4334784591792</v>
       </c>
       <c r="D4" t="n">
-        <v>102.3953038052381</v>
+        <v>111.5206487162122</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.95146206079796</v>
+        <v>36.66827675361837</v>
       </c>
       <c r="C5" t="n">
-        <v>150.4037482906114</v>
+        <v>153.5453409442012</v>
       </c>
       <c r="D5" t="n">
-        <v>71.37305809874313</v>
+        <v>74.22012644105888</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.34474197957343</v>
+        <v>36.02523200733671</v>
       </c>
       <c r="C6" t="n">
-        <v>132.6292061052229</v>
+        <v>126.269444477112</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.73883941513712</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>104.6817942084289</v>
+        <v>116.1800233205675</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>67.59332943739288</v>
+        <v>93.6292785540183</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>50.36562072326985</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.198755004614362</v>
+        <v>5.235660506748239</v>
       </c>
       <c r="C2" t="n">
-        <v>6.137886646951058</v>
+        <v>8.408669086873932</v>
       </c>
       <c r="D2" t="n">
-        <v>17.22476347101029</v>
+        <v>19.10677382005142</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.65873701401638</v>
+        <v>19.81657741022187</v>
       </c>
       <c r="C3" t="n">
-        <v>29.43770491184061</v>
+        <v>28.73575530330414</v>
       </c>
       <c r="D3" t="n">
-        <v>67.49515466696822</v>
+        <v>74.89262361846794</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.90299657039137</v>
+        <v>39.44956799974958</v>
       </c>
       <c r="C4" t="n">
-        <v>116.5108722968987</v>
+        <v>121.9860792434832</v>
       </c>
       <c r="D4" t="n">
-        <v>111.5844623169882</v>
+        <v>123.8494363861436</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.33911353525522</v>
+        <v>42.92691836819179</v>
       </c>
       <c r="C5" t="n">
-        <v>191.5880644837651</v>
+        <v>203.0008815456343</v>
       </c>
       <c r="D5" t="n">
-        <v>89.68265278294614</v>
+        <v>93.48692513690253</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.63029169278902</v>
+        <v>42.62650357069227</v>
       </c>
       <c r="C6" t="n">
-        <v>182.7425176685013</v>
+        <v>180.4884249395506</v>
       </c>
       <c r="D6" t="n">
-        <v>49.10702016642546</v>
+        <v>48.90576188705487</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.41672835715293</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="C7" t="n">
-        <v>146.4826479598496</v>
+        <v>148.1594730387031</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>100.3886114977576</v>
+        <v>121.9183386518901</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>78.4328058399819</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.674681656995811</v>
+        <v>3.127848185730338</v>
       </c>
       <c r="C2" t="n">
-        <v>2.852958828541231</v>
+        <v>3.948589266480671</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87227498745668</v>
+        <v>13.30955362647401</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.79265561242145</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="C3" t="n">
-        <v>28.92228736711104</v>
+        <v>32.32895190084746</v>
       </c>
       <c r="D3" t="n">
-        <v>68.60943831128834</v>
+        <v>75.35895377798516</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.81664383014665</v>
+        <v>43.64850293081319</v>
       </c>
       <c r="C4" t="n">
-        <v>112.9500733735955</v>
+        <v>116.893753901555</v>
       </c>
       <c r="D4" t="n">
-        <v>119.5101115333727</v>
+        <v>132.6174251327719</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.86711387369075</v>
+        <v>44.76769531365456</v>
       </c>
       <c r="C5" t="n">
-        <v>225.6547098211294</v>
+        <v>238.8837601358552</v>
       </c>
       <c r="D5" t="n">
-        <v>94.64047868939254</v>
+        <v>98.91108120286617</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="C6" t="n">
-        <v>219.089762922831</v>
+        <v>214.4205708414332</v>
       </c>
       <c r="D6" t="n">
-        <v>48.58374864006191</v>
+        <v>48.22148373719484</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>145.5843488104638</v>
+        <v>156.4238252130528</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>74.01886816168827</v>
+        <v>94.79755832207201</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.190099201725387</v>
+        <v>3.468514639103981</v>
       </c>
       <c r="C2" t="n">
-        <v>6.163412087261475</v>
+        <v>9.052695580859838</v>
       </c>
       <c r="D2" t="n">
-        <v>10.63919987092268</v>
+        <v>11.6356737907332</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38813450054276</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>19.58586669972387</v>
+        <v>23.72393327312417</v>
       </c>
       <c r="D3" t="n">
-        <v>62.73858703989242</v>
+        <v>69.81698798751192</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.80464187351743</v>
+        <v>41.91277298970483</v>
       </c>
       <c r="C4" t="n">
-        <v>93.56350145783378</v>
+        <v>100.1363023377662</v>
       </c>
       <c r="D4" t="n">
-        <v>126.6317093799791</v>
+        <v>138.3095983219949</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.76451339083034</v>
+        <v>53.55433726666352</v>
       </c>
       <c r="C5" t="n">
-        <v>219.2978934361313</v>
+        <v>229.9743997198154</v>
       </c>
       <c r="D5" t="n">
-        <v>111.2074711985575</v>
+        <v>118.3742294395592</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.21268906558563</v>
+        <v>44.75984133202059</v>
       </c>
       <c r="C6" t="n">
-        <v>282.9691407950583</v>
+        <v>287.7993394999525</v>
       </c>
       <c r="D6" t="n">
-        <v>62.26931163726245</v>
+        <v>62.91333813124836</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>220.8019309190373</v>
+        <v>223.1375087074405</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>122.0852357616121</v>
+        <v>140.0266750567226</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>51.9187455913883</v>
+        <v>63.89999457401638</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.040472640052371</v>
+        <v>2.399391389179204</v>
       </c>
       <c r="C2" t="n">
-        <v>3.134720419660066</v>
+        <v>4.611268966847269</v>
       </c>
       <c r="D2" t="n">
-        <v>8.209374302911829</v>
+        <v>8.715956118303183</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.83206438931157</v>
+        <v>14.27461161974862</v>
       </c>
       <c r="C3" t="n">
-        <v>21.99605731364979</v>
+        <v>29.36898257254333</v>
       </c>
       <c r="D3" t="n">
-        <v>58.17836895366599</v>
+        <v>65.29113107093413</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.64399510291945</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>76.21896476690537</v>
+        <v>84.83380087167113</v>
       </c>
       <c r="D4" t="n">
-        <v>128.890710847451</v>
+        <v>140.823854192571</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.84505776030758</v>
+        <v>58.63488163614076</v>
       </c>
       <c r="C5" t="n">
-        <v>208.7931930006905</v>
+        <v>220.7214276072892</v>
       </c>
       <c r="D5" t="n">
-        <v>125.1973759840745</v>
+        <v>131.4805612912541</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.83283481950012</v>
+        <v>52.20639766873265</v>
       </c>
       <c r="C6" t="n">
-        <v>318.4308496201572</v>
+        <v>326.5616841067293</v>
       </c>
       <c r="D6" t="n">
-        <v>73.09700706740053</v>
+        <v>75.31084814047708</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>284.8806035752267</v>
+        <v>286.5574286540802</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>42.93869934064274</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>163.8095131921015</v>
+        <v>179.7481871705485</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>61.23749480009903</v>
+        <v>72.33124385808797</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.117449871611123</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C2" t="n">
-        <v>5.785439221126453</v>
+        <v>9.534733703645022</v>
       </c>
       <c r="D2" t="n">
-        <v>8.988881980083795</v>
+        <v>13.13283903970958</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.67574552015807</v>
+        <v>11.3588209381356</v>
       </c>
       <c r="C3" t="n">
-        <v>17.33766445699867</v>
+        <v>24.18535469412017</v>
       </c>
       <c r="D3" t="n">
-        <v>52.39587497565228</v>
+        <v>58.50234569606743</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.90077103307561</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="C4" t="n">
-        <v>66.58311104972293</v>
+        <v>79.56279744757001</v>
       </c>
       <c r="D4" t="n">
-        <v>128.1887612389145</v>
+        <v>140.7089897111741</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.01057221169781</v>
+        <v>58.46307578789757</v>
       </c>
       <c r="C5" t="n">
-        <v>179.3407618732861</v>
+        <v>193.453385121834</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8619213688584</v>
+        <v>146.2067768549562</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.1032984642535</v>
+        <v>61.86679507852126</v>
       </c>
       <c r="C6" t="n">
-        <v>324.9516178717645</v>
+        <v>337.1076179457486</v>
       </c>
       <c r="D6" t="n">
-        <v>88.63414623481054</v>
+        <v>91.8542787047401</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.08788393395925</v>
+        <v>31.79978988825843</v>
       </c>
       <c r="C7" t="n">
-        <v>355.0677104472396</v>
+        <v>358.660907044783</v>
       </c>
       <c r="D7" t="n">
-        <v>51.74203100462389</v>
+        <v>50.60418541540184</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>247.5918622725243</v>
+        <v>256.687754752371</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>112.3796779574281</v>
+        <v>124.4718644306361</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>50.96252332745193</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3711,7 +3711,7 @@
         <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.546874528994478</v>
+        <v>5.969026041820607</v>
       </c>
       <c r="C2" t="n">
-        <v>2.195187866695868</v>
+        <v>8.948630324209677</v>
       </c>
       <c r="D2" t="n">
-        <v>10.24355554611122</v>
+        <v>8.660978246865362</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.949170103557418</v>
+        <v>2.368957210347553</v>
       </c>
       <c r="C2" t="n">
-        <v>3.332051708213675</v>
+        <v>5.568472978487908</v>
       </c>
       <c r="D2" t="n">
-        <v>6.615016031215008</v>
+        <v>9.770353152664256</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.30468594568178</v>
+        <v>15.17291076913446</v>
       </c>
       <c r="C3" t="n">
-        <v>21.45609607631404</v>
+        <v>31.4257440129404</v>
       </c>
       <c r="D3" t="n">
-        <v>56.48485416384024</v>
+        <v>63.47489781807752</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.23781359526853</v>
+        <v>44.55465606183299</v>
       </c>
       <c r="C4" t="n">
-        <v>97.78796182920779</v>
+        <v>114.6475151542383</v>
       </c>
       <c r="D4" t="n">
-        <v>131.647458400976</v>
+        <v>143.8613815895106</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="C5" t="n">
-        <v>270.6923857534518</v>
+        <v>285.7376693210342</v>
       </c>
       <c r="D5" t="n">
-        <v>125.7373372214103</v>
+        <v>133.2477071588984</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.62772199810799</v>
+        <v>19.72331137831842</v>
       </c>
       <c r="C6" t="n">
-        <v>297.5402402214894</v>
+        <v>298.9892998329577</v>
       </c>
       <c r="D6" t="n">
-        <v>73.05675541152641</v>
+        <v>73.09700706740053</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.707300315414209</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>174.0903751509741</v>
+        <v>180.4982424165931</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>91.70996179221579</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4319,7 +4319,7 @@
         <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.740679737358599</v>
+        <v>7.160867754776235</v>
       </c>
       <c r="C2" t="n">
-        <v>6.062292073724055</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="D2" t="n">
-        <v>10.76584532477052</v>
+        <v>11.03680769114264</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.78588118948296</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C3" t="n">
-        <v>5.615596868291756</v>
+        <v>22.545836028028</v>
       </c>
       <c r="D3" t="n">
-        <v>11.74170254279185</v>
+        <v>10.41143440353742</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3989152244815</v>
+        <v>13.39795409716713</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14726205757964</v>
+        <v>70.14223027340438</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576342967586059</v>
+        <v>1.576229893784368</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.17421131200819</v>
+        <v>4.80467326458389</v>
       </c>
       <c r="C2" t="n">
-        <v>4.957825906446392</v>
+        <v>4.25685804561417</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5585576904542</v>
+        <v>21.37166577374881</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6679325962531</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0824100538945</v>
+        <v>21.26465527398591</v>
       </c>
       <c r="D3" t="n">
-        <v>17.94634803363169</v>
+        <v>17.16585860875548</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.73268688700438</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="C4" t="n">
-        <v>9.240209392370978</v>
+        <v>34.89327690434013</v>
       </c>
       <c r="D4" t="n">
-        <v>21.22440361811179</v>
+        <v>20.52245400957532</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44523165531515</v>
+        <v>15.44104548326866</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16813449807402</v>
+        <v>86.14478006455148</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251627716908454</v>
+        <v>3.250746417530245</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.426119561372121</v>
+        <v>4.195989687950868</v>
       </c>
       <c r="C2" t="n">
-        <v>5.098215828153687</v>
+        <v>4.873395603881167</v>
       </c>
       <c r="D2" t="n">
-        <v>17.48787185574843</v>
+        <v>22.1914251067949</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.45962215650353</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4224956701914</v>
+        <v>18.41267819314893</v>
       </c>
       <c r="D3" t="n">
-        <v>27.82763867687584</v>
+        <v>30.27709919897163</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.34225440035042</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="C4" t="n">
-        <v>28.8692729910817</v>
+        <v>45.71606359595697</v>
       </c>
       <c r="D4" t="n">
-        <v>25.25742318715769</v>
+        <v>24.5171854181556</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.32093368829747</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="C5" t="n">
-        <v>12.17367153266045</v>
+        <v>39.04901493641689</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74458414468146</v>
+        <v>16.73383699321817</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1419632825569</v>
+        <v>102.0764056586308</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023375243404439</v>
+        <v>5.020151097965451</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.699847244407733</v>
+        <v>6.372524348266047</v>
       </c>
       <c r="C2" t="n">
-        <v>10.62349190765473</v>
+        <v>4.185190463204153</v>
       </c>
       <c r="D2" t="n">
-        <v>20.11895570312988</v>
+        <v>20.05906909317083</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65458903902115</v>
+        <v>16.04175748739288</v>
       </c>
       <c r="C3" t="n">
-        <v>19.22752878767378</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D3" t="n">
-        <v>34.92567457858028</v>
+        <v>40.40873550679871</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.41280136633594</v>
+        <v>32.03442758957343</v>
       </c>
       <c r="C4" t="n">
-        <v>38.67104207028186</v>
+        <v>45.92026711844031</v>
       </c>
       <c r="D4" t="n">
-        <v>32.82571623919635</v>
+        <v>33.65529304928491</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.21266370338984</v>
+        <v>27.4889357189107</v>
       </c>
       <c r="C5" t="n">
-        <v>34.68023765251858</v>
+        <v>63.17546476828226</v>
       </c>
       <c r="D5" t="n">
-        <v>32.81491701444964</v>
+        <v>31.6122760767473</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27046364475338</v>
+        <v>11.75348351524281</v>
       </c>
       <c r="C6" t="n">
-        <v>16.06041069377357</v>
+        <v>38.40007970390975</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08011704485779</v>
+        <v>18.05933422924556</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9512397688342</v>
+        <v>117.8156566384115</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887663636136302</v>
+        <v>6.879746373045927</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.501534208149878</v>
+        <v>6.764241682260523</v>
       </c>
       <c r="C2" t="n">
-        <v>8.91721439767378</v>
+        <v>13.22708681931728</v>
       </c>
       <c r="D2" t="n">
-        <v>21.91849924501429</v>
+        <v>19.74098283699486</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.03885330200914</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="C3" t="n">
-        <v>30.19365064411065</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="D3" t="n">
-        <v>39.93258787023902</v>
+        <v>43.90375733391736</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.21462719879833</v>
+        <v>22.75593003673682</v>
       </c>
       <c r="C4" t="n">
-        <v>36.92254940901829</v>
+        <v>38.46683854779853</v>
       </c>
       <c r="D4" t="n">
-        <v>36.71834588653496</v>
+        <v>39.84521232456105</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.78283813537898</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="C5" t="n">
-        <v>40.49709280018094</v>
+        <v>55.81235698643118</v>
       </c>
       <c r="D5" t="n">
-        <v>30.26237298340794</v>
+        <v>29.20699420134261</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.88052987971816</v>
+        <v>13.28304643845935</v>
       </c>
       <c r="C6" t="n">
-        <v>24.91577498607981</v>
+        <v>48.02022545782425</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.95352336719769</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>14.31289978021425</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.070497245652699</v>
+        <v>7.058884207678765</v>
       </c>
       <c r="C21" t="n">
-        <v>67.16972383370063</v>
+        <v>66.17703944698842</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302872934239525</v>
+        <v>5.294163155759074</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.896376711706344</v>
+        <v>5.412375093512666</v>
       </c>
       <c r="C2" t="n">
-        <v>7.502515955854125</v>
+        <v>7.034222300928397</v>
       </c>
       <c r="D2" t="n">
-        <v>18.29781371175205</v>
+        <v>21.3441768380299</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.44551783574558</v>
+        <v>21.22047662729481</v>
       </c>
       <c r="C3" t="n">
-        <v>33.32542582065798</v>
+        <v>39.47607518776425</v>
       </c>
       <c r="D3" t="n">
-        <v>49.1855599827652</v>
+        <v>50.24584750335175</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.87600635629119</v>
+        <v>29.67332436085984</v>
       </c>
       <c r="C4" t="n">
-        <v>62.09063355508952</v>
+        <v>39.98560224626834</v>
       </c>
       <c r="D4" t="n">
-        <v>49.77460860531329</v>
+        <v>54.31813698056752</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.30579086657305</v>
+        <v>29.7960428238907</v>
       </c>
       <c r="C5" t="n">
-        <v>58.09492039880502</v>
+        <v>65.4580281806561</v>
       </c>
       <c r="D5" t="n">
-        <v>37.18369429834795</v>
+        <v>37.87091769132071</v>
       </c>
     </row>
     <row r="6">
@@ -6126,10 +6126,10 @@
         <v>24.0704902127233</v>
       </c>
       <c r="C6" t="n">
-        <v>48.86551023118075</v>
+        <v>72.45298057341462</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>33.44912603139308</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>27.42806736124739</v>
+        <v>51.2030515149924</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>19.3600647277471</v>
+        <v>27.20422888467911</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.298081746353026</v>
+        <v>7.283147055421548</v>
       </c>
       <c r="C21" t="n">
-        <v>77.5421185550009</v>
+        <v>75.56265069999857</v>
       </c>
       <c r="D21" t="n">
-        <v>6.385821528058898</v>
+        <v>6.372753673493854</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.916592502868026</v>
+        <v>4.34619708670063</v>
       </c>
       <c r="C2" t="n">
-        <v>6.604216806468294</v>
+        <v>11.20959528709008</v>
       </c>
       <c r="D2" t="n">
-        <v>18.2526533173567</v>
+        <v>25.55980148006571</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.20222433154161</v>
+        <v>20.04237938219863</v>
       </c>
       <c r="C3" t="n">
-        <v>30.80233422074368</v>
+        <v>32.13751109851934</v>
       </c>
       <c r="D3" t="n">
-        <v>52.41060119121597</v>
+        <v>55.66018609227291</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.65301075870693</v>
+        <v>36.16954891986099</v>
       </c>
       <c r="C4" t="n">
-        <v>74.94269275138453</v>
+        <v>74.25350586300326</v>
       </c>
       <c r="D4" t="n">
-        <v>62.77982044347079</v>
+        <v>66.78731457220626</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.11130701014094</v>
+        <v>38.18998569520093</v>
       </c>
       <c r="C5" t="n">
-        <v>90.44350725373742</v>
+        <v>70.44039777970866</v>
       </c>
       <c r="D5" t="n">
-        <v>47.27115195948392</v>
+        <v>49.48008429403926</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.94472869558847</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C6" t="n">
-        <v>73.6605302496382</v>
+        <v>90.36496743739767</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.90042687571034</v>
       </c>
       <c r="C7" t="n">
-        <v>51.80191761458295</v>
+        <v>81.08646988456105</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>29.12354564648163</v>
+        <v>49.4015444776995</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>24.51718541815559</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.513436828787759</v>
+        <v>7.494967491831674</v>
       </c>
       <c r="C21" t="n">
-        <v>87.34370313465769</v>
+        <v>85.25525521958528</v>
       </c>
       <c r="D21" t="n">
-        <v>7.513436828787759</v>
+        <v>7.494967491831674</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_33_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628164228</v>
+        <v>10.84497637142587</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907176568981</v>
+        <v>37.78907207853869</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.300455855228529</v>
+        <v>0.9434595437811848</v>
       </c>
       <c r="C2" t="n">
-        <v>10.9101622372948</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="D2" t="n">
-        <v>29.63110920957723</v>
+        <v>16.51594162854409</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.21494599396782</v>
+        <v>8.46757394912874</v>
       </c>
       <c r="C3" t="n">
-        <v>38.54341486872978</v>
+        <v>37.50767104074939</v>
       </c>
       <c r="D3" t="n">
-        <v>62.70422587024377</v>
+        <v>72.13882130805563</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.6755498981756</v>
+        <v>17.17862132891069</v>
       </c>
       <c r="C4" t="n">
-        <v>77.6101012638231</v>
+        <v>100.5829975431985</v>
       </c>
       <c r="D4" t="n">
-        <v>78.96294960027521</v>
+        <v>70.70546965985528</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.16668579220627</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="C5" t="n">
-        <v>105.7833151325938</v>
+        <v>94.61593499678636</v>
       </c>
       <c r="D5" t="n">
-        <v>61.60466844148736</v>
+        <v>43.93320976504477</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.82776185006286</v>
+        <v>14.16858286768997</v>
       </c>
       <c r="C6" t="n">
-        <v>100.8303979646687</v>
+        <v>61.26302024040947</v>
       </c>
       <c r="D6" t="n">
-        <v>44.27682146153116</v>
+        <v>29.02144388523996</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.12296480940488</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>107.1970318267092</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>78.77543578876406</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.47216389248049</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.69202780418958</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.22734060132234</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.653531279713278</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.520768251607315</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54397034361074</v>
+        <v>5.366232951413066</v>
       </c>
       <c r="D2" t="n">
-        <v>26.27549555646164</v>
+        <v>15.66869335977909</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.41129553481718</v>
+        <v>5.630323083855458</v>
       </c>
       <c r="C3" t="n">
-        <v>40.3203782134165</v>
+        <v>23.75338570425158</v>
       </c>
       <c r="D3" t="n">
-        <v>70.11151229878597</v>
+        <v>69.30647918130357</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.27615850899639</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C4" t="n">
-        <v>86.09731016703677</v>
+        <v>97.74967366874218</v>
       </c>
       <c r="D4" t="n">
-        <v>90.27071965778997</v>
+        <v>89.86231261282329</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.70726892434777</v>
+        <v>23.24287689804324</v>
       </c>
       <c r="C5" t="n">
-        <v>124.0192787389783</v>
+        <v>144.8077863764046</v>
       </c>
       <c r="D5" t="n">
-        <v>72.99294181075037</v>
+        <v>58.48761948050374</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>20.60884780754905</v>
       </c>
       <c r="C6" t="n">
-        <v>131.6229147083699</v>
+        <v>108.9612324512408</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>35.62271544859552</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.18391528252619</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>126.420633623566</v>
+        <v>63.30014672672159</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.61594102565702</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>108.3996727644116</v>
+        <v>38.97047512007713</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.872942479898646</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3482522386824</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.841178099873309</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.875580083467912</v>
+        <v>0.7588909753827844</v>
       </c>
       <c r="C2" t="n">
-        <v>9.911724822075797</v>
+        <v>2.165735435568464</v>
       </c>
       <c r="D2" t="n">
-        <v>28.52173430377833</v>
+        <v>10.56655054080842</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.10481032464293</v>
+        <v>5.856125055832224</v>
       </c>
       <c r="C3" t="n">
-        <v>40.30074325933157</v>
+        <v>23.95464398362218</v>
       </c>
       <c r="D3" t="n">
-        <v>74.0237769002095</v>
+        <v>68.57507714163971</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.57871672835365</v>
+        <v>18.64633414675967</v>
       </c>
       <c r="C4" t="n">
-        <v>92.56800928572751</v>
+        <v>91.5214662330004</v>
       </c>
       <c r="D4" t="n">
-        <v>99.90657337497241</v>
+        <v>101.8465068385641</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.8362787842316</v>
+        <v>24.17553721707771</v>
       </c>
       <c r="C5" t="n">
-        <v>137.7882902910399</v>
+        <v>174.6529165855076</v>
       </c>
       <c r="D5" t="n">
-        <v>84.55302102825655</v>
+        <v>68.01057221169781</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.48565598509524</v>
+        <v>16.26166897314417</v>
       </c>
       <c r="C6" t="n">
-        <v>160.0405837554981</v>
+        <v>144.9462128027034</v>
       </c>
       <c r="D6" t="n">
-        <v>61.34352355215771</v>
+        <v>36.50825187782615</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.0471335564664</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>153.0102884453866</v>
+        <v>63.12048689684442</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05280305851362</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.87734795689393</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>133.8514819970101</v>
+        <v>39.80496066868692</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.64062358698343</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>98.73436661610168</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>59.50372835439919</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.037506100052498</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5157088757219</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05157088757218</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.154977268550754</v>
+        <v>0.7520187414530567</v>
       </c>
       <c r="C2" t="n">
-        <v>6.739697989654353</v>
+        <v>5.719662124941918</v>
       </c>
       <c r="D2" t="n">
-        <v>23.52758373227481</v>
+        <v>10.27497147264712</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04652735719387</v>
+        <v>4.138066573400306</v>
       </c>
       <c r="C3" t="n">
-        <v>59.33192250615598</v>
+        <v>15.05510104462484</v>
       </c>
       <c r="D3" t="n">
-        <v>79.31048828757858</v>
+        <v>61.35432277690442</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.90006702281185</v>
+        <v>15.20039970485337</v>
       </c>
       <c r="C4" t="n">
-        <v>119.4335352124415</v>
+        <v>74.7767773893668</v>
       </c>
       <c r="D4" t="n">
-        <v>95.60553668266714</v>
+        <v>113.6647857022872</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.93763547748049</v>
+        <v>26.5808190924824</v>
       </c>
       <c r="C5" t="n">
-        <v>95.62222639363934</v>
+        <v>173.3766445699867</v>
       </c>
       <c r="D5" t="n">
-        <v>59.37119241432587</v>
+        <v>86.78649705541805</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.43025184083414</v>
+        <v>23.74847696573035</v>
       </c>
       <c r="C6" t="n">
-        <v>100.7498946529204</v>
+        <v>214.1790609061884</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30949687321178</v>
+        <v>47.53720558733482</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>94.08186424567607</v>
+        <v>133.0680473290212</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>72.76713983877357</v>
+        <v>60.33330516448773</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>45.37343364717482</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.493459242337651</v>
+        <v>0.4231332605303753</v>
       </c>
       <c r="C2" t="n">
-        <v>4.010439371848221</v>
+        <v>2.935425635697963</v>
       </c>
       <c r="D2" t="n">
-        <v>16.45016453235955</v>
+        <v>7.13141532364883</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.40624792757571</v>
+        <v>3.485204350076177</v>
       </c>
       <c r="C3" t="n">
-        <v>43.36379609658162</v>
+        <v>19.26679869584365</v>
       </c>
       <c r="D3" t="n">
-        <v>79.95353303386024</v>
+        <v>56.46031047123407</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.25964872447344</v>
+        <v>12.62233023350124</v>
       </c>
       <c r="C4" t="n">
-        <v>136.4334784591792</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="D4" t="n">
-        <v>111.5206487162122</v>
+        <v>118.3359412790935</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.66827675361837</v>
+        <v>27.09623663721197</v>
       </c>
       <c r="C5" t="n">
-        <v>153.5453409442012</v>
+        <v>163.9273229166112</v>
       </c>
       <c r="D5" t="n">
-        <v>74.22012644105888</v>
+        <v>103.5252954128262</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.02523200733671</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="C6" t="n">
-        <v>126.269444477112</v>
+        <v>248.5539750226863</v>
       </c>
       <c r="D6" t="n">
-        <v>37.23278168356029</v>
+        <v>58.32464936159877</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>116.1800233205675</v>
+        <v>199.7817308234089</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>93.6292785540183</v>
+        <v>91.29271901791088</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>50.36562072326985</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.235660506748239</v>
+        <v>0.6224280444924778</v>
       </c>
       <c r="C2" t="n">
-        <v>8.408669086873932</v>
+        <v>6.490334072775664</v>
       </c>
       <c r="D2" t="n">
-        <v>19.10677382005142</v>
+        <v>8.222137023067036</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.81657741022187</v>
+        <v>2.449460522095792</v>
       </c>
       <c r="C3" t="n">
-        <v>28.73575530330414</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="D3" t="n">
-        <v>74.89262361846794</v>
+        <v>49.8335134675681</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.44956799974958</v>
+        <v>9.801769079200154</v>
       </c>
       <c r="C4" t="n">
-        <v>121.9860792434832</v>
+        <v>53.20778032706438</v>
       </c>
       <c r="D4" t="n">
-        <v>123.8494363861436</v>
+        <v>119.3824843318206</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.92691836819179</v>
+        <v>24.07736244665303</v>
       </c>
       <c r="C5" t="n">
-        <v>203.0008815456343</v>
+        <v>137.9846398318892</v>
       </c>
       <c r="D5" t="n">
-        <v>93.48692513690253</v>
+        <v>119.4296082216245</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>32.24157635516951</v>
       </c>
       <c r="C6" t="n">
-        <v>180.4884249395506</v>
+        <v>255.1149949301677</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>73.58002693788995</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>148.1594730387031</v>
+        <v>274.9394263220235</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>121.9183386518901</v>
+        <v>167.3143524962627</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>78.4328058399819</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.127848185730338</v>
+        <v>0.4123340357836604</v>
       </c>
       <c r="C2" t="n">
-        <v>3.948589266480671</v>
+        <v>3.374266859496287</v>
       </c>
       <c r="D2" t="n">
-        <v>13.30955362647401</v>
+        <v>5.919938656608266</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.54797944988574</v>
+        <v>3.534291735288518</v>
       </c>
       <c r="C3" t="n">
-        <v>32.32895190084746</v>
+        <v>21.02412708644545</v>
       </c>
       <c r="D3" t="n">
-        <v>75.35895377798516</v>
+        <v>52.85238765812704</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.64850293081319</v>
+        <v>16.31075635835651</v>
       </c>
       <c r="C4" t="n">
-        <v>116.893753901555</v>
+        <v>75.79779500178348</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6174251327719</v>
+        <v>123.8239109458332</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.76769531365456</v>
+        <v>19.92947839621025</v>
       </c>
       <c r="C5" t="n">
-        <v>238.8837601358552</v>
+        <v>210.8303194870026</v>
       </c>
       <c r="D5" t="n">
-        <v>98.91108120286617</v>
+        <v>109.3666942530947</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.22019888985433</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>214.4205708414332</v>
+        <v>246.098624014365</v>
       </c>
       <c r="D6" t="n">
-        <v>48.22148373719484</v>
+        <v>62.95358978712248</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>156.4238252130528</v>
+        <v>117.6173019595849</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>94.79755832207201</v>
+        <v>55.99398031171682</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.468514639103981</v>
+        <v>0.2395464398362217</v>
       </c>
       <c r="C2" t="n">
-        <v>9.052695580859838</v>
+        <v>2.024363766156923</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6356737907332</v>
+        <v>4.765403356414017</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80613803837365</v>
+        <v>2.474004214701962</v>
       </c>
       <c r="C3" t="n">
-        <v>23.72393327312417</v>
+        <v>16.66025854106837</v>
       </c>
       <c r="D3" t="n">
-        <v>69.81698798751192</v>
+        <v>45.71508184825273</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.91277298970483</v>
+        <v>10.88660029239288</v>
       </c>
       <c r="C4" t="n">
-        <v>100.1363023377662</v>
+        <v>61.50354842794993</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3095983219949</v>
+        <v>117.4297881480737</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.55433726666352</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="C5" t="n">
-        <v>229.9743997198154</v>
+        <v>159.6076330179252</v>
       </c>
       <c r="D5" t="n">
-        <v>118.3742294395592</v>
+        <v>114.2999764669349</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.75984133202059</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>287.7993394999525</v>
+        <v>237.9275378719188</v>
       </c>
       <c r="D6" t="n">
-        <v>62.91333813124836</v>
+        <v>67.70328518026855</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>223.1375087074405</v>
+        <v>163.131125528467</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>140.0266750567226</v>
+        <v>63.75469591378786</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>63.89999457401638</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.399391389179204</v>
+        <v>0.170824100538945</v>
       </c>
       <c r="C2" t="n">
-        <v>4.611268966847269</v>
+        <v>4.058545009356314</v>
       </c>
       <c r="D2" t="n">
-        <v>8.715956118303183</v>
+        <v>8.020878743696441</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.27461161974862</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C3" t="n">
-        <v>29.36898257254333</v>
+        <v>11.41281706186917</v>
       </c>
       <c r="D3" t="n">
-        <v>65.29113107093413</v>
+        <v>38.92138773486479</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>7.632106652814704</v>
       </c>
       <c r="C4" t="n">
-        <v>84.83380087167113</v>
+        <v>49.91499852702059</v>
       </c>
       <c r="D4" t="n">
-        <v>140.823854192571</v>
+        <v>114.1242436278747</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.63488163614076</v>
+        <v>17.62237129123025</v>
       </c>
       <c r="C5" t="n">
-        <v>220.7214276072892</v>
+        <v>135.1866588747858</v>
       </c>
       <c r="D5" t="n">
-        <v>131.4805612912541</v>
+        <v>131.1614932873739</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.20639766873265</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>326.5616841067293</v>
+        <v>247.5879352817074</v>
       </c>
       <c r="D6" t="n">
-        <v>75.31084814047708</v>
+        <v>87.42659655858698</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>286.5574286540802</v>
+        <v>261.8841453509494</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>179.7481871705485</v>
+        <v>142.8639259219958</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>55.02499532762521</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.274128593663113</v>
+        <v>0.3445934441906304</v>
       </c>
       <c r="C2" t="n">
-        <v>9.534733703645022</v>
+        <v>10.61563792602076</v>
       </c>
       <c r="D2" t="n">
-        <v>13.13283903970958</v>
+        <v>7.936448441131216</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.3588209381356</v>
+        <v>1.035743827980385</v>
       </c>
       <c r="C3" t="n">
-        <v>24.18535469412017</v>
+        <v>13.96536109291088</v>
       </c>
       <c r="D3" t="n">
-        <v>58.50234569606743</v>
+        <v>36.4130223505142</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.76190263842031</v>
+        <v>5.258240703945916</v>
       </c>
       <c r="C4" t="n">
-        <v>79.56279744757001</v>
+        <v>37.89251614081414</v>
       </c>
       <c r="D4" t="n">
-        <v>140.7089897111741</v>
+        <v>107.3217137851486</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.46307578789757</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="C5" t="n">
-        <v>193.453385121834</v>
+        <v>112.4101121362598</v>
       </c>
       <c r="D5" t="n">
-        <v>146.2067768549562</v>
+        <v>142.427048193606</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.86679507852126</v>
+        <v>21.37362926915731</v>
       </c>
       <c r="C6" t="n">
-        <v>337.1076179457486</v>
+        <v>232.252054393668</v>
       </c>
       <c r="D6" t="n">
-        <v>91.8542787047401</v>
+        <v>107.0694046251572</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.79978988825843</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="C7" t="n">
-        <v>358.660907044783</v>
+        <v>312.9075370360646</v>
       </c>
       <c r="D7" t="n">
-        <v>50.60418541540184</v>
+        <v>57.9103518304066</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>256.687754752371</v>
+        <v>245.004957071834</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>124.4718644306361</v>
+        <v>114.487490278446</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>50.96252332745193</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.969026041820607</v>
+        <v>6.104507225006667</v>
       </c>
       <c r="C2" t="n">
-        <v>8.948630324209677</v>
+        <v>6.722026530977911</v>
       </c>
       <c r="D2" t="n">
-        <v>8.660978246865362</v>
+        <v>4.889103567149116</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.368957210347553</v>
+        <v>0.3082687791334984</v>
       </c>
       <c r="C2" t="n">
-        <v>5.568472978487908</v>
+        <v>9.068403544127788</v>
       </c>
       <c r="D2" t="n">
-        <v>9.770353152664256</v>
+        <v>12.58404207303562</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.17291076913446</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C3" t="n">
-        <v>31.4257440129404</v>
+        <v>28.06816686441631</v>
       </c>
       <c r="D3" t="n">
-        <v>63.47489781807752</v>
+        <v>34.4102570338507</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.55465606183299</v>
+        <v>3.624612524079224</v>
       </c>
       <c r="C4" t="n">
-        <v>114.6475151542383</v>
+        <v>35.99087083768807</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8613815895106</v>
+        <v>101.9868967602714</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.93196597543326</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>285.7376693210342</v>
+        <v>91.84249773228912</v>
       </c>
       <c r="D5" t="n">
-        <v>133.2477071588984</v>
+        <v>146.5503885514426</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.72331137831842</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C6" t="n">
-        <v>298.9892998329577</v>
+        <v>206.5714979459799</v>
       </c>
       <c r="D6" t="n">
-        <v>73.09700706740053</v>
+        <v>125.0618948008885</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>180.4982424165931</v>
+        <v>327.1605502063198</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>72.22325161062085</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>91.70996179221579</v>
+        <v>325.3659154029567</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>198.1343581756827</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>85.12734343524093</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.160867754776235</v>
+        <v>4.732023934469626</v>
       </c>
       <c r="C2" t="n">
-        <v>5.257258956241669</v>
+        <v>6.368597357449058</v>
       </c>
       <c r="D2" t="n">
-        <v>11.03680769114264</v>
+        <v>12.87169415037993</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.67927160034756</v>
+        <v>10.07273144557228</v>
       </c>
       <c r="C3" t="n">
-        <v>22.545836028028</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D3" t="n">
-        <v>10.41143440353742</v>
+        <v>6.405903770210438</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39795409716713</v>
+        <v>11.6786621261782</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14223027340438</v>
+        <v>59.95046558104808</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576229893784368</v>
+        <v>0.7785774750785465</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80467326458389</v>
+        <v>3.408628029144925</v>
       </c>
       <c r="C2" t="n">
-        <v>4.25685804561417</v>
+        <v>6.668030407244336</v>
       </c>
       <c r="D2" t="n">
-        <v>21.37166577374881</v>
+        <v>17.93162181806799</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.90002596508285</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C3" t="n">
-        <v>21.26465527398591</v>
+        <v>21.01430960940298</v>
       </c>
       <c r="D3" t="n">
-        <v>17.16585860875548</v>
+        <v>16.12029730373262</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.75370449942107</v>
+        <v>12.4181267110179</v>
       </c>
       <c r="C4" t="n">
-        <v>34.89327690434013</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D4" t="n">
-        <v>20.52245400957532</v>
+        <v>17.51045205294611</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44104548326866</v>
+        <v>13.63169335657916</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14478006455148</v>
+        <v>73.77151698854604</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250746417530245</v>
+        <v>1.603728630185783</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.195989687950868</v>
+        <v>1.644427404613408</v>
       </c>
       <c r="C2" t="n">
-        <v>4.873395603881167</v>
+        <v>4.095851422117692</v>
       </c>
       <c r="D2" t="n">
-        <v>22.1914251067949</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.05924901962008</v>
+        <v>12.88052987971815</v>
       </c>
       <c r="C3" t="n">
-        <v>18.41267819314893</v>
+        <v>24.26389451045992</v>
       </c>
       <c r="D3" t="n">
-        <v>30.27709919897163</v>
+        <v>27.2876774395401</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.2566624236317</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="C4" t="n">
-        <v>45.71606359595697</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="D4" t="n">
-        <v>24.5171854181556</v>
+        <v>21.72214970416493</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.88543861823939</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="C5" t="n">
-        <v>39.04901493641689</v>
+        <v>26.89988709636261</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>26.35992585902687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73383699321817</v>
+        <v>14.84549916917929</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0764056586308</v>
+        <v>87.42349510738919</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020151097965451</v>
+        <v>2.474249861529882</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.372524348266047</v>
+        <v>1.174170254279185</v>
       </c>
       <c r="C2" t="n">
-        <v>4.185190463204153</v>
+        <v>3.859250225394212</v>
       </c>
       <c r="D2" t="n">
-        <v>20.05906909317083</v>
+        <v>21.43057063600362</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.04175748739288</v>
+        <v>8.771915737445251</v>
       </c>
       <c r="C3" t="n">
-        <v>18.69247628885927</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="D3" t="n">
-        <v>40.40873550679871</v>
+        <v>40.44800541496859</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.03442758957343</v>
+        <v>23.7769476491535</v>
       </c>
       <c r="C4" t="n">
-        <v>45.92026711844031</v>
+        <v>52.99081408442584</v>
       </c>
       <c r="D4" t="n">
-        <v>33.65529304928491</v>
+        <v>30.29869764846506</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.4889357189107</v>
+        <v>22.50656611985813</v>
       </c>
       <c r="C5" t="n">
-        <v>63.17546476828226</v>
+        <v>55.59146375297565</v>
       </c>
       <c r="D5" t="n">
-        <v>31.6122760767473</v>
+        <v>28.49522711576368</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.75348351524281</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="C6" t="n">
-        <v>38.40007970390975</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05933422924556</v>
+        <v>16.09312355837189</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8156566384115</v>
+        <v>101.6407803686646</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879746373045927</v>
+        <v>3.38802601228882</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.764241682260523</v>
+        <v>2.143155238370787</v>
       </c>
       <c r="C2" t="n">
-        <v>13.22708681931728</v>
+        <v>11.58167766699962</v>
       </c>
       <c r="D2" t="n">
-        <v>19.74098283699486</v>
+        <v>32.61954922130452</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18549356284042</v>
+        <v>6.135923151542565</v>
       </c>
       <c r="C3" t="n">
-        <v>16.24792450528471</v>
+        <v>16.69952844923824</v>
       </c>
       <c r="D3" t="n">
-        <v>43.90375733391736</v>
+        <v>47.73748211900116</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.75593003673682</v>
+        <v>20.25443688631594</v>
       </c>
       <c r="C4" t="n">
-        <v>38.46683854779853</v>
+        <v>50.11920204950392</v>
       </c>
       <c r="D4" t="n">
-        <v>39.84521232456105</v>
+        <v>42.72958707963818</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.36559536107409</v>
+        <v>29.550605897829</v>
       </c>
       <c r="C5" t="n">
-        <v>55.81235698643118</v>
+        <v>78.34346679889548</v>
       </c>
       <c r="D5" t="n">
-        <v>29.20699420134261</v>
+        <v>33.03581024790518</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.28304643845935</v>
+        <v>20.48809283992669</v>
       </c>
       <c r="C6" t="n">
-        <v>48.02022545782425</v>
+        <v>60.57874209054944</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.61339669317178</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058884207678765</v>
+        <v>17.37030105992276</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17703944698842</v>
+        <v>115.5125020484863</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294163155759074</v>
+        <v>4.342575264980689</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.412375093512666</v>
+        <v>2.044980467946106</v>
       </c>
       <c r="C2" t="n">
-        <v>7.034222300928397</v>
+        <v>11.7426842904961</v>
       </c>
       <c r="D2" t="n">
-        <v>21.3441768380299</v>
+        <v>30.80037072533518</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.22047662729481</v>
+        <v>6.729880512611885</v>
       </c>
       <c r="C3" t="n">
-        <v>39.47607518776425</v>
+        <v>32.38785676310228</v>
       </c>
       <c r="D3" t="n">
-        <v>50.24584750335175</v>
+        <v>61.0647072041516</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.67332436085984</v>
+        <v>15.94063747385546</v>
       </c>
       <c r="C4" t="n">
-        <v>39.98560224626834</v>
+        <v>45.6011991145601</v>
       </c>
       <c r="D4" t="n">
-        <v>54.31813698056752</v>
+        <v>55.08390018988003</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.7960428238907</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="C5" t="n">
-        <v>65.4580281806561</v>
+        <v>85.70657458074656</v>
       </c>
       <c r="D5" t="n">
-        <v>37.87091769132071</v>
+        <v>40.5216364927871</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.0704902127233</v>
+        <v>30.14849024971531</v>
       </c>
       <c r="C6" t="n">
-        <v>72.45298057341462</v>
+        <v>91.93478201648833</v>
       </c>
       <c r="D6" t="n">
-        <v>33.44912603139308</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>51.2030515149924</v>
+        <v>58.86853758975149</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>27.20422888467911</v>
+        <v>32.7952820603647</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.283147055421548</v>
+        <v>18.66835234216377</v>
       </c>
       <c r="C21" t="n">
-        <v>75.56265069999857</v>
+        <v>128.900528076845</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372753673493854</v>
+        <v>5.333814954903933</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.34619708670063</v>
+        <v>1.841758693167016</v>
       </c>
       <c r="C2" t="n">
-        <v>11.20959528709008</v>
+        <v>7.139269305282806</v>
       </c>
       <c r="D2" t="n">
-        <v>25.55980148006571</v>
+        <v>24.01747583669397</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.04237938219863</v>
+        <v>9.92056055141402</v>
       </c>
       <c r="C3" t="n">
-        <v>32.13751109851934</v>
+        <v>48.08600255400877</v>
       </c>
       <c r="D3" t="n">
-        <v>55.66018609227291</v>
+        <v>67.62769060704153</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>14.44739921569606</v>
       </c>
       <c r="C4" t="n">
-        <v>74.25350586300326</v>
+        <v>71.67543639165113</v>
       </c>
       <c r="D4" t="n">
-        <v>66.78731457220626</v>
+        <v>51.49757582626644</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.18998569520093</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>70.44039777970866</v>
+        <v>54.92878405260905</v>
       </c>
       <c r="D5" t="n">
-        <v>49.48008429403926</v>
+        <v>34.7538687303371</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>90.36496743739767</v>
+        <v>38.76234460677682</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>25.27803988894688</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90042687571034</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>81.08646988456105</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4015444776995</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.494967491831674</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.25525521958528</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.494967491831674</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
